--- a/Briefing/Ori.xlsx
+++ b/Briefing/Ori.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ngt_VKHL\Briefing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A419E6F-C1CE-4C30-8977-B402A91CF53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71ED0644-7ECD-4B01-B47C-495297092654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4425" yWindow="4020" windowWidth="20160" windowHeight="17100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1065" yWindow="2805" windowWidth="20160" windowHeight="17100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ori Format" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Ori Format'!$A$1:$V$1124</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Ori Format'!$A$1:$V$1123</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -788,179 +788,179 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="12" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="4" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="12" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="5" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="20" fontId="13" fillId="6" borderId="12" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="12" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="9" fillId="5" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="12" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="12" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="12" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="3" borderId="12" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="12" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="10" fontId="9" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="12" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="13" fillId="6" borderId="12" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="12" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="4" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="3" borderId="12" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="12" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="4" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="12" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="10" fontId="9" fillId="5" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="4" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="3" borderId="12" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="12" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="10" fillId="3" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1433,7 +1433,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V607"/>
+  <dimension ref="A1:V606"/>
   <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.7109375" style="1" customWidth="1"/>
@@ -1462,109 +1462,109 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="336" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47"/>
-      <c r="B1" s="30"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="65" t="s">
+      <c r="A1" s="79"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="65" t="s">
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="31"/>
-      <c r="J1" s="65" t="s">
+      <c r="I1" s="45"/>
+      <c r="J1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="31"/>
-      <c r="L1" s="65" t="s">
+      <c r="K1" s="45"/>
+      <c r="L1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="30"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="44"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="29" t="s">
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="T1" s="30"/>
-      <c r="U1" s="31"/>
-      <c r="V1" s="70" t="s">
+      <c r="T1" s="44"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="66" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="306.60000000000002" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="23"/>
-      <c r="V2" s="28"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="46"/>
+      <c r="T2" s="47"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="37"/>
     </row>
     <row r="3" spans="1:22" s="2" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="55" t="s">
+      <c r="B3" s="44"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="55" t="s">
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="26"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="24"/>
     </row>
     <row r="4" spans="1:22" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="32"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="78" t="s">
+      <c r="A4" s="46"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="26"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="24"/>
       <c r="H4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1578,287 +1578,287 @@
         <v>14</v>
       </c>
       <c r="L4" s="4"/>
-      <c r="M4" s="58">
+      <c r="M4" s="50">
         <f>D4+1</f>
         <v>46229</v>
       </c>
-      <c r="N4" s="31"/>
-      <c r="O4" s="58">
+      <c r="N4" s="45"/>
+      <c r="O4" s="50">
         <f>M4+1</f>
         <v>46230</v>
       </c>
-      <c r="P4" s="31"/>
-      <c r="Q4" s="58">
+      <c r="P4" s="45"/>
+      <c r="Q4" s="50">
         <f>O4+1</f>
         <v>46231</v>
       </c>
-      <c r="R4" s="31"/>
-      <c r="S4" s="58">
+      <c r="R4" s="45"/>
+      <c r="S4" s="50">
         <f>Q4+1</f>
         <v>46232</v>
       </c>
-      <c r="T4" s="31"/>
-      <c r="U4" s="58">
+      <c r="T4" s="45"/>
+      <c r="U4" s="50">
         <f>S4+1</f>
         <v>46233</v>
       </c>
-      <c r="V4" s="31"/>
+      <c r="V4" s="45"/>
     </row>
     <row r="5" spans="1:22" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="31"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="45"/>
       <c r="D5" s="20" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="14"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="38" t="s">
+      <c r="F5" s="53"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="45">
+      <c r="I5" s="38"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="69">
         <v>205427.65</v>
       </c>
       <c r="L5" s="20" t="s">
         <v>16</v>
       </c>
       <c r="M5" s="15"/>
-      <c r="N5" s="37"/>
+      <c r="N5" s="36"/>
       <c r="O5" s="15"/>
-      <c r="P5" s="37"/>
+      <c r="P5" s="36"/>
       <c r="Q5" s="15"/>
-      <c r="R5" s="37"/>
+      <c r="R5" s="36"/>
       <c r="S5" s="15"/>
-      <c r="T5" s="37"/>
+      <c r="T5" s="36"/>
       <c r="U5" s="15"/>
-      <c r="V5" s="37"/>
+      <c r="V5" s="36"/>
     </row>
     <row r="6" spans="1:22" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="28"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="23"/>
+      <c r="A6" s="37"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="48"/>
       <c r="D6" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="85">
+      <c r="E6" s="21">
         <f>F5-E5</f>
         <v>0</v>
       </c>
-      <c r="F6" s="32"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
       <c r="L6" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="M6" s="85">
+      <c r="M6" s="21">
         <f>N5-M5</f>
         <v>0</v>
       </c>
-      <c r="N6" s="28"/>
-      <c r="O6" s="85">
+      <c r="N6" s="37"/>
+      <c r="O6" s="21">
         <f>P5-O5</f>
         <v>0</v>
       </c>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="85">
+      <c r="P6" s="37"/>
+      <c r="Q6" s="21">
         <f>R5-Q5</f>
         <v>0</v>
       </c>
-      <c r="R6" s="28"/>
-      <c r="S6" s="85">
+      <c r="R6" s="37"/>
+      <c r="S6" s="21">
         <f>T5-S5</f>
         <v>0</v>
       </c>
-      <c r="T6" s="28"/>
-      <c r="U6" s="85">
+      <c r="T6" s="37"/>
+      <c r="U6" s="21">
         <f>V5-U5</f>
         <v>0</v>
       </c>
-      <c r="V6" s="28"/>
+      <c r="V6" s="37"/>
     </row>
     <row r="7" spans="1:22" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="31"/>
+      <c r="B7" s="53"/>
+      <c r="C7" s="45"/>
       <c r="D7" s="20" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="14"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="38" t="s">
+      <c r="F7" s="53"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="45">
+      <c r="I7" s="38"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="69">
         <v>29000</v>
       </c>
       <c r="L7" s="20" t="s">
         <v>20</v>
       </c>
       <c r="M7" s="15"/>
-      <c r="N7" s="37"/>
+      <c r="N7" s="36"/>
       <c r="O7" s="15"/>
-      <c r="P7" s="37"/>
+      <c r="P7" s="36"/>
       <c r="Q7" s="15"/>
-      <c r="R7" s="37"/>
+      <c r="R7" s="36"/>
       <c r="S7" s="15"/>
-      <c r="T7" s="37"/>
+      <c r="T7" s="36"/>
       <c r="U7" s="15"/>
-      <c r="V7" s="37"/>
+      <c r="V7" s="36"/>
     </row>
     <row r="8" spans="1:22" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="28"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="23"/>
+      <c r="A8" s="37"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="48"/>
       <c r="D8" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="85">
+      <c r="E8" s="21">
         <f>F7-E7</f>
         <v>0</v>
       </c>
-      <c r="F8" s="32"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="37"/>
       <c r="L8" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="M8" s="85">
+      <c r="M8" s="21">
         <f>N7-M7</f>
         <v>0</v>
       </c>
-      <c r="N8" s="28"/>
-      <c r="O8" s="85">
+      <c r="N8" s="37"/>
+      <c r="O8" s="21">
         <f>P7-O7</f>
         <v>0</v>
       </c>
-      <c r="P8" s="28"/>
-      <c r="Q8" s="85">
+      <c r="P8" s="37"/>
+      <c r="Q8" s="21">
         <f>R7-Q7</f>
         <v>0</v>
       </c>
-      <c r="R8" s="28"/>
-      <c r="S8" s="85">
+      <c r="R8" s="37"/>
+      <c r="S8" s="21">
         <f>T7-S7</f>
         <v>0</v>
       </c>
-      <c r="T8" s="28"/>
-      <c r="U8" s="85">
+      <c r="T8" s="37"/>
+      <c r="U8" s="21">
         <f>V7-U7</f>
         <v>0</v>
       </c>
-      <c r="V8" s="28"/>
+      <c r="V8" s="37"/>
     </row>
     <row r="9" spans="1:22" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="27" t="s">
+      <c r="B9" s="53"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="41"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="38" t="s">
+      <c r="E9" s="53"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="29" t="s">
         <v>24</v>
       </c>
       <c r="I9" s="42"/>
       <c r="J9" s="42"/>
-      <c r="K9" s="45">
+      <c r="K9" s="69">
         <v>160368</v>
       </c>
-      <c r="L9" s="27" t="s">
+      <c r="L9" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="M9" s="37"/>
-      <c r="N9" s="31"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="31"/>
-      <c r="Q9" s="37"/>
-      <c r="R9" s="31"/>
-      <c r="S9" s="37"/>
-      <c r="T9" s="31"/>
-      <c r="U9" s="37"/>
-      <c r="V9" s="31"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="45"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="45"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="45"/>
+      <c r="S9" s="36"/>
+      <c r="T9" s="45"/>
+      <c r="U9" s="36"/>
+      <c r="V9" s="45"/>
     </row>
     <row r="10" spans="1:22" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28"/>
-      <c r="B10" s="32"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="43"/>
-      <c r="K10" s="43"/>
-      <c r="L10" s="28"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="32"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="32"/>
-      <c r="R10" s="23"/>
-      <c r="S10" s="32"/>
-      <c r="T10" s="23"/>
-      <c r="U10" s="32"/>
-      <c r="V10" s="23"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="37"/>
+      <c r="M10" s="46"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="46"/>
+      <c r="P10" s="48"/>
+      <c r="Q10" s="46"/>
+      <c r="R10" s="48"/>
+      <c r="S10" s="46"/>
+      <c r="T10" s="48"/>
+      <c r="U10" s="46"/>
+      <c r="V10" s="48"/>
     </row>
     <row r="11" spans="1:22" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="76"/>
-      <c r="C11" s="26"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="24"/>
       <c r="D11" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="71"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="28"/>
-      <c r="K11" s="28"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="37"/>
       <c r="L11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M11" s="34"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="34"/>
-      <c r="P11" s="26"/>
-      <c r="Q11" s="34"/>
-      <c r="R11" s="26"/>
-      <c r="S11" s="34"/>
-      <c r="T11" s="26"/>
-      <c r="U11" s="34"/>
-      <c r="V11" s="26"/>
+      <c r="M11" s="55"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="55"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="55"/>
+      <c r="R11" s="24"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="24"/>
+      <c r="U11" s="55"/>
+      <c r="V11" s="24"/>
     </row>
     <row r="12" spans="1:22" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="72"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="81" t="s">
+      <c r="B12" s="70"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="56" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="18"/>
@@ -1866,95 +1866,95 @@
         <f>E12+E13</f>
         <v>0</v>
       </c>
-      <c r="G12" s="33"/>
-      <c r="H12" s="38" t="s">
+      <c r="G12" s="54"/>
+      <c r="H12" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="I12" s="54"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="52">
+      <c r="I12" s="84"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="83">
         <v>180414</v>
       </c>
-      <c r="L12" s="79" t="s">
+      <c r="L12" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="M12" s="37"/>
-      <c r="N12" s="31"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="31"/>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="31"/>
-      <c r="S12" s="37"/>
-      <c r="T12" s="31"/>
-      <c r="U12" s="37"/>
-      <c r="V12" s="31"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="45"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="45"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="45"/>
+      <c r="S12" s="36"/>
+      <c r="T12" s="45"/>
+      <c r="U12" s="36"/>
+      <c r="V12" s="45"/>
     </row>
     <row r="13" spans="1:22" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="28"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="37"/>
       <c r="E13" s="18"/>
       <c r="F13" s="87"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="80"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="32"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="32"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="32"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="32"/>
-      <c r="V13" s="23"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="64"/>
+      <c r="M13" s="46"/>
+      <c r="N13" s="48"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="48"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="48"/>
+      <c r="S13" s="46"/>
+      <c r="T13" s="48"/>
+      <c r="U13" s="46"/>
+      <c r="V13" s="48"/>
     </row>
     <row r="14" spans="1:22" s="2" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="80" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="30"/>
-      <c r="O14" s="30"/>
-      <c r="P14" s="30"/>
-      <c r="Q14" s="30"/>
-      <c r="R14" s="30"/>
-      <c r="S14" s="30"/>
-      <c r="T14" s="30"/>
-      <c r="U14" s="30"/>
-      <c r="V14" s="31"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="44"/>
+      <c r="N14" s="44"/>
+      <c r="O14" s="44"/>
+      <c r="P14" s="44"/>
+      <c r="Q14" s="44"/>
+      <c r="R14" s="44"/>
+      <c r="S14" s="44"/>
+      <c r="T14" s="44"/>
+      <c r="U14" s="44"/>
+      <c r="V14" s="45"/>
     </row>
     <row r="15" spans="1:22" ht="96" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="26"/>
+      <c r="B15" s="24"/>
       <c r="C15" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="26"/>
-      <c r="F15" s="24" t="s">
+      <c r="E15" s="24"/>
+      <c r="F15" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="G15" s="26"/>
+      <c r="G15" s="24"/>
       <c r="H15" s="13" t="s">
         <v>36</v>
       </c>
@@ -1967,90 +1967,90 @@
       <c r="K15" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L15" s="24" t="s">
+      <c r="L15" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="M15" s="26"/>
-      <c r="N15" s="24" t="s">
+      <c r="M15" s="24"/>
+      <c r="N15" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="O15" s="26"/>
-      <c r="P15" s="24" t="s">
+      <c r="O15" s="24"/>
+      <c r="P15" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="Q15" s="25"/>
-      <c r="R15" s="25"/>
-      <c r="S15" s="25"/>
-      <c r="T15" s="25"/>
-      <c r="U15" s="25"/>
-      <c r="V15" s="26"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23"/>
+      <c r="U15" s="23"/>
+      <c r="V15" s="24"/>
     </row>
     <row r="16" spans="1:22" ht="114" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="67"/>
-      <c r="B16" s="26"/>
+      <c r="A16" s="72"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="26"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="24"/>
       <c r="H16" s="8"/>
       <c r="I16" s="9"/>
       <c r="J16" s="9"/>
       <c r="K16" s="8"/>
-      <c r="L16" s="61"/>
-      <c r="M16" s="26"/>
-      <c r="N16" s="41"/>
-      <c r="O16" s="26"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="25"/>
-      <c r="R16" s="25"/>
-      <c r="S16" s="25"/>
-      <c r="T16" s="25"/>
-      <c r="U16" s="25"/>
-      <c r="V16" s="26"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="53"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="62"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="23"/>
+      <c r="U16" s="23"/>
+      <c r="V16" s="24"/>
     </row>
     <row r="17" spans="1:22" s="2" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A17" s="74" t="s">
+      <c r="A17" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="25"/>
-      <c r="N17" s="25"/>
-      <c r="O17" s="25"/>
-      <c r="P17" s="25"/>
-      <c r="Q17" s="25"/>
-      <c r="R17" s="25"/>
-      <c r="S17" s="25"/>
-      <c r="T17" s="25"/>
-      <c r="U17" s="25"/>
-      <c r="V17" s="26"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
+      <c r="S17" s="23"/>
+      <c r="T17" s="23"/>
+      <c r="U17" s="23"/>
+      <c r="V17" s="24"/>
     </row>
     <row r="18" spans="1:22" ht="96" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="26"/>
+      <c r="B18" s="24"/>
       <c r="C18" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="E18" s="26"/>
-      <c r="F18" s="24" t="s">
+      <c r="E18" s="24"/>
+      <c r="F18" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="G18" s="26"/>
+      <c r="G18" s="24"/>
       <c r="H18" s="13" t="s">
         <v>36</v>
       </c>
@@ -2063,90 +2063,90 @@
       <c r="K18" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L18" s="24" t="s">
+      <c r="L18" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="M18" s="26"/>
-      <c r="N18" s="24" t="s">
+      <c r="M18" s="24"/>
+      <c r="N18" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="O18" s="26"/>
-      <c r="P18" s="24" t="s">
+      <c r="O18" s="24"/>
+      <c r="P18" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="Q18" s="25"/>
-      <c r="R18" s="25"/>
-      <c r="S18" s="25"/>
-      <c r="T18" s="25"/>
-      <c r="U18" s="25"/>
-      <c r="V18" s="26"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
+      <c r="S18" s="23"/>
+      <c r="T18" s="23"/>
+      <c r="U18" s="23"/>
+      <c r="V18" s="24"/>
     </row>
     <row r="19" spans="1:22" ht="114" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="67"/>
-      <c r="B19" s="26"/>
+      <c r="A19" s="72"/>
+      <c r="B19" s="24"/>
       <c r="C19" s="7"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="26"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="24"/>
       <c r="H19" s="8"/>
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
       <c r="K19" s="8"/>
-      <c r="L19" s="61"/>
-      <c r="M19" s="26"/>
-      <c r="N19" s="41"/>
-      <c r="O19" s="26"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="25"/>
-      <c r="R19" s="25"/>
-      <c r="S19" s="25"/>
-      <c r="T19" s="25"/>
-      <c r="U19" s="25"/>
-      <c r="V19" s="26"/>
+      <c r="L19" s="52"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="53"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="62"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
+      <c r="S19" s="23"/>
+      <c r="T19" s="23"/>
+      <c r="U19" s="23"/>
+      <c r="V19" s="24"/>
     </row>
     <row r="20" spans="1:22" s="2" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A20" s="74" t="s">
+      <c r="A20" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="25"/>
-      <c r="N20" s="25"/>
-      <c r="O20" s="25"/>
-      <c r="P20" s="25"/>
-      <c r="Q20" s="25"/>
-      <c r="R20" s="25"/>
-      <c r="S20" s="25"/>
-      <c r="T20" s="25"/>
-      <c r="U20" s="25"/>
-      <c r="V20" s="26"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="23"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="23"/>
+      <c r="Q20" s="23"/>
+      <c r="R20" s="23"/>
+      <c r="S20" s="23"/>
+      <c r="T20" s="23"/>
+      <c r="U20" s="23"/>
+      <c r="V20" s="24"/>
     </row>
     <row r="21" spans="1:22" ht="96" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="26"/>
+      <c r="B21" s="24"/>
       <c r="C21" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="26"/>
-      <c r="F21" s="24" t="s">
+      <c r="E21" s="24"/>
+      <c r="F21" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="G21" s="26"/>
+      <c r="G21" s="24"/>
       <c r="H21" s="13" t="s">
         <v>36</v>
       </c>
@@ -2159,772 +2159,885 @@
       <c r="K21" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L21" s="24" t="s">
+      <c r="L21" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="M21" s="26"/>
-      <c r="N21" s="24" t="s">
+      <c r="M21" s="24"/>
+      <c r="N21" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="O21" s="26"/>
-      <c r="P21" s="24" t="s">
+      <c r="O21" s="24"/>
+      <c r="P21" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="Q21" s="25"/>
-      <c r="R21" s="25"/>
-      <c r="S21" s="25"/>
-      <c r="T21" s="25"/>
-      <c r="U21" s="25"/>
-      <c r="V21" s="26"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
+      <c r="S21" s="23"/>
+      <c r="T21" s="23"/>
+      <c r="U21" s="23"/>
+      <c r="V21" s="24"/>
     </row>
     <row r="22" spans="1:22" ht="114" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="67"/>
-      <c r="B22" s="26"/>
+      <c r="A22" s="72"/>
+      <c r="B22" s="24"/>
       <c r="C22" s="7"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="26"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="24"/>
       <c r="H22" s="8"/>
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
       <c r="K22" s="8"/>
-      <c r="L22" s="61"/>
-      <c r="M22" s="26"/>
-      <c r="N22" s="41"/>
-      <c r="O22" s="26"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="25"/>
-      <c r="R22" s="25"/>
-      <c r="S22" s="25"/>
-      <c r="T22" s="25"/>
-      <c r="U22" s="25"/>
-      <c r="V22" s="26"/>
+      <c r="L22" s="52"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="53"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="62"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
+      <c r="S22" s="23"/>
+      <c r="T22" s="23"/>
+      <c r="U22" s="23"/>
+      <c r="V22" s="24"/>
     </row>
     <row r="23" spans="1:22" ht="103.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="63" t="s">
+      <c r="A23" s="75" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="25"/>
-      <c r="N23" s="25"/>
-      <c r="O23" s="25"/>
-      <c r="P23" s="25"/>
-      <c r="Q23" s="25"/>
-      <c r="R23" s="25"/>
-      <c r="S23" s="25"/>
-      <c r="T23" s="25"/>
-      <c r="U23" s="25"/>
-      <c r="V23" s="26"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="23"/>
+      <c r="P23" s="23"/>
+      <c r="Q23" s="23"/>
+      <c r="R23" s="23"/>
+      <c r="S23" s="23"/>
+      <c r="T23" s="23"/>
+      <c r="U23" s="23"/>
+      <c r="V23" s="24"/>
     </row>
     <row r="24" spans="1:22" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="38" t="s">
+      <c r="A24" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="25"/>
-      <c r="N24" s="25"/>
-      <c r="O24" s="26"/>
-      <c r="P24" s="38" t="s">
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="23"/>
+      <c r="O24" s="24"/>
+      <c r="P24" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="Q24" s="25"/>
-      <c r="R24" s="25"/>
-      <c r="S24" s="25"/>
-      <c r="T24" s="25"/>
-      <c r="U24" s="25"/>
-      <c r="V24" s="26"/>
+      <c r="Q24" s="23"/>
+      <c r="R24" s="23"/>
+      <c r="S24" s="23"/>
+      <c r="T24" s="23"/>
+      <c r="U24" s="23"/>
+      <c r="V24" s="24"/>
     </row>
     <row r="25" spans="1:22" ht="114" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="39"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="25"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="25"/>
-      <c r="N25" s="25"/>
-      <c r="O25" s="26"/>
-      <c r="P25" s="59"/>
-      <c r="Q25" s="25"/>
-      <c r="R25" s="25"/>
-      <c r="S25" s="25"/>
-      <c r="T25" s="25"/>
-      <c r="U25" s="25"/>
-      <c r="V25" s="26"/>
+      <c r="A25" s="58"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="23"/>
+      <c r="N25" s="23"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="57"/>
+      <c r="Q25" s="23"/>
+      <c r="R25" s="23"/>
+      <c r="S25" s="23"/>
+      <c r="T25" s="23"/>
+      <c r="U25" s="23"/>
+      <c r="V25" s="24"/>
     </row>
     <row r="26" spans="1:22" ht="114" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="39"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="25"/>
-      <c r="J26" s="25"/>
-      <c r="K26" s="25"/>
-      <c r="L26" s="25"/>
-      <c r="M26" s="25"/>
-      <c r="N26" s="25"/>
-      <c r="O26" s="26"/>
-      <c r="P26" s="59"/>
-      <c r="Q26" s="25"/>
-      <c r="R26" s="25"/>
-      <c r="S26" s="25"/>
-      <c r="T26" s="25"/>
-      <c r="U26" s="25"/>
-      <c r="V26" s="26"/>
+      <c r="A26" s="58"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="23"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="23"/>
+      <c r="M26" s="23"/>
+      <c r="N26" s="23"/>
+      <c r="O26" s="24"/>
+      <c r="P26" s="57"/>
+      <c r="Q26" s="23"/>
+      <c r="R26" s="23"/>
+      <c r="S26" s="23"/>
+      <c r="T26" s="23"/>
+      <c r="U26" s="23"/>
+      <c r="V26" s="24"/>
     </row>
     <row r="27" spans="1:22" ht="114" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="39"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25"/>
-      <c r="J27" s="25"/>
-      <c r="K27" s="25"/>
-      <c r="L27" s="25"/>
-      <c r="M27" s="25"/>
-      <c r="N27" s="25"/>
-      <c r="O27" s="26"/>
-      <c r="P27" s="59"/>
-      <c r="Q27" s="25"/>
-      <c r="R27" s="25"/>
-      <c r="S27" s="25"/>
-      <c r="T27" s="25"/>
-      <c r="U27" s="25"/>
-      <c r="V27" s="26"/>
+      <c r="A27" s="58"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="23"/>
+      <c r="J27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
+      <c r="M27" s="23"/>
+      <c r="N27" s="23"/>
+      <c r="O27" s="24"/>
+      <c r="P27" s="57"/>
+      <c r="Q27" s="23"/>
+      <c r="R27" s="23"/>
+      <c r="S27" s="23"/>
+      <c r="T27" s="23"/>
+      <c r="U27" s="23"/>
+      <c r="V27" s="24"/>
     </row>
     <row r="28" spans="1:22" ht="103.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="63" t="s">
+      <c r="A28" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="B28" s="25"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25"/>
-      <c r="I28" s="25"/>
-      <c r="J28" s="25"/>
-      <c r="K28" s="25"/>
-      <c r="L28" s="25"/>
-      <c r="M28" s="25"/>
-      <c r="N28" s="25"/>
-      <c r="O28" s="25"/>
-      <c r="P28" s="25"/>
-      <c r="Q28" s="25"/>
-      <c r="R28" s="25"/>
-      <c r="S28" s="25"/>
-      <c r="T28" s="25"/>
-      <c r="U28" s="25"/>
-      <c r="V28" s="26"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="23"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="23"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="23"/>
+      <c r="S28" s="23"/>
+      <c r="T28" s="23"/>
+      <c r="U28" s="23"/>
+      <c r="V28" s="24"/>
     </row>
     <row r="29" spans="1:22" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="38" t="s">
+      <c r="A29" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="B29" s="25"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="38" t="s">
+      <c r="B29" s="23"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
-      <c r="I29" s="25"/>
-      <c r="J29" s="25"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="38" t="s">
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="23"/>
+      <c r="J29" s="23"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="M29" s="25"/>
-      <c r="N29" s="25"/>
-      <c r="O29" s="26"/>
-      <c r="P29" s="38" t="s">
+      <c r="M29" s="23"/>
+      <c r="N29" s="23"/>
+      <c r="O29" s="24"/>
+      <c r="P29" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="Q29" s="26"/>
-      <c r="R29" s="38" t="s">
+      <c r="Q29" s="24"/>
+      <c r="R29" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="S29" s="25"/>
-      <c r="T29" s="25"/>
-      <c r="U29" s="26"/>
+      <c r="S29" s="23"/>
+      <c r="T29" s="23"/>
+      <c r="U29" s="24"/>
       <c r="V29" s="12" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:22" s="10" customFormat="1" ht="117" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A30" s="60"/>
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="60"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="25"/>
-      <c r="J30" s="25"/>
-      <c r="K30" s="26"/>
-      <c r="L30" s="60"/>
-      <c r="M30" s="25"/>
-      <c r="N30" s="25"/>
-      <c r="O30" s="26"/>
-      <c r="P30" s="60"/>
-      <c r="Q30" s="26"/>
-      <c r="R30" s="60"/>
-      <c r="S30" s="25"/>
-      <c r="T30" s="25"/>
-      <c r="U30" s="26"/>
+      <c r="A30" s="26"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="23"/>
+      <c r="I30" s="23"/>
+      <c r="J30" s="23"/>
+      <c r="K30" s="24"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="23"/>
+      <c r="N30" s="23"/>
+      <c r="O30" s="24"/>
+      <c r="P30" s="26"/>
+      <c r="Q30" s="24"/>
+      <c r="R30" s="26"/>
+      <c r="S30" s="23"/>
+      <c r="T30" s="23"/>
+      <c r="U30" s="24"/>
       <c r="V30" s="17"/>
     </row>
-    <row r="31" spans="1:22" s="10" customFormat="1" ht="117" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A31" s="60"/>
-      <c r="B31" s="25"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="60"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="25"/>
-      <c r="J31" s="25"/>
-      <c r="K31" s="26"/>
-      <c r="L31" s="60"/>
-      <c r="M31" s="25"/>
-      <c r="N31" s="25"/>
-      <c r="O31" s="26"/>
-      <c r="P31" s="60"/>
-      <c r="Q31" s="26"/>
-      <c r="R31" s="60"/>
-      <c r="S31" s="25"/>
-      <c r="T31" s="25"/>
-      <c r="U31" s="26"/>
-      <c r="V31" s="17"/>
-    </row>
-    <row r="32" spans="1:22" s="10" customFormat="1" ht="103.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A32" s="63" t="s">
+    <row r="31" spans="1:22" s="10" customFormat="1" ht="103.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A31" s="75" t="s">
         <v>53</v>
       </c>
-      <c r="B32" s="25"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="25"/>
-      <c r="J32" s="25"/>
-      <c r="K32" s="25"/>
-      <c r="L32" s="25"/>
-      <c r="M32" s="25"/>
-      <c r="N32" s="25"/>
-      <c r="O32" s="25"/>
-      <c r="P32" s="25"/>
-      <c r="Q32" s="25"/>
-      <c r="R32" s="25"/>
-      <c r="S32" s="25"/>
-      <c r="T32" s="25"/>
-      <c r="U32" s="25"/>
-      <c r="V32" s="26"/>
-    </row>
-    <row r="33" spans="1:22" s="10" customFormat="1" ht="87.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="38" t="s">
+      <c r="B31" s="23"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23"/>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23"/>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="24"/>
+    </row>
+    <row r="32" spans="1:22" s="10" customFormat="1" ht="87.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A32" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="B33" s="25"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="38" t="s">
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="25"/>
-      <c r="J33" s="26"/>
-      <c r="K33" s="38" t="s">
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="23"/>
+      <c r="I32" s="23"/>
+      <c r="J32" s="24"/>
+      <c r="K32" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="L33" s="26"/>
-      <c r="M33" s="38" t="s">
+      <c r="L32" s="24"/>
+      <c r="M32" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="N33" s="25"/>
-      <c r="O33" s="25"/>
-      <c r="P33" s="25"/>
-      <c r="Q33" s="25"/>
-      <c r="R33" s="25"/>
-      <c r="S33" s="25"/>
-      <c r="T33" s="25"/>
-      <c r="U33" s="26"/>
-      <c r="V33" s="12" t="s">
+      <c r="N32" s="23"/>
+      <c r="O32" s="23"/>
+      <c r="P32" s="23"/>
+      <c r="Q32" s="23"/>
+      <c r="R32" s="23"/>
+      <c r="S32" s="23"/>
+      <c r="T32" s="23"/>
+      <c r="U32" s="24"/>
+      <c r="V32" s="12" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:22" s="10" customFormat="1" ht="114" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="62"/>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="62"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="62"/>
-      <c r="L34" s="26"/>
-      <c r="M34" s="62"/>
-      <c r="N34" s="25"/>
-      <c r="O34" s="25"/>
-      <c r="P34" s="25"/>
-      <c r="Q34" s="25"/>
-      <c r="R34" s="25"/>
-      <c r="S34" s="25"/>
-      <c r="T34" s="25"/>
-      <c r="U34" s="26"/>
-      <c r="V34" s="16"/>
-    </row>
-    <row r="35" spans="1:22" s="10" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A35" s="83" t="s">
+    <row r="33" spans="1:22" s="10" customFormat="1" ht="114" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A33" s="28"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="24"/>
+      <c r="M33" s="28"/>
+      <c r="N33" s="23"/>
+      <c r="O33" s="23"/>
+      <c r="P33" s="23"/>
+      <c r="Q33" s="23"/>
+      <c r="R33" s="23"/>
+      <c r="S33" s="23"/>
+      <c r="T33" s="23"/>
+      <c r="U33" s="24"/>
+      <c r="V33" s="16"/>
+    </row>
+    <row r="34" spans="1:22" s="10" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A34" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="38" t="s">
+      <c r="B34" s="23"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="38" t="s">
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="24"/>
+      <c r="K34" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L35" s="25"/>
-      <c r="M35" s="25"/>
-      <c r="N35" s="25"/>
-      <c r="O35" s="26"/>
-      <c r="P35" s="38" t="s">
+      <c r="L34" s="23"/>
+      <c r="M34" s="23"/>
+      <c r="N34" s="23"/>
+      <c r="O34" s="24"/>
+      <c r="P34" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="Q35" s="25"/>
-      <c r="R35" s="25"/>
-      <c r="S35" s="25"/>
-      <c r="T35" s="25"/>
-      <c r="U35" s="25"/>
-      <c r="V35" s="26"/>
+      <c r="Q34" s="23"/>
+      <c r="R34" s="23"/>
+      <c r="S34" s="23"/>
+      <c r="T34" s="23"/>
+      <c r="U34" s="23"/>
+      <c r="V34" s="24"/>
+    </row>
+    <row r="35" spans="1:22" ht="114" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="78" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="44"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="23"/>
+      <c r="I35" s="23"/>
+      <c r="J35" s="24"/>
+      <c r="K35" s="71" t="s">
+        <v>62</v>
+      </c>
+      <c r="L35" s="44"/>
+      <c r="M35" s="44"/>
+      <c r="N35" s="44"/>
+      <c r="O35" s="44"/>
+      <c r="P35" s="76" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q35" s="44"/>
+      <c r="R35" s="44"/>
+      <c r="S35" s="44"/>
+      <c r="T35" s="44"/>
+      <c r="U35" s="44"/>
+      <c r="V35" s="45"/>
     </row>
     <row r="36" spans="1:22" ht="114" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="50" t="s">
-        <v>60</v>
-      </c>
-      <c r="B36" s="30"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="25"/>
-      <c r="I36" s="25"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="73" t="s">
-        <v>62</v>
-      </c>
-      <c r="L36" s="30"/>
-      <c r="M36" s="30"/>
-      <c r="N36" s="30"/>
-      <c r="O36" s="30"/>
-      <c r="P36" s="66" t="s">
+      <c r="A36" s="46"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="65" t="s">
+        <v>64</v>
+      </c>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="23"/>
+      <c r="I36" s="23"/>
+      <c r="J36" s="24"/>
+      <c r="K36" s="67" t="s">
+        <v>65</v>
+      </c>
+      <c r="L36" s="23"/>
+      <c r="M36" s="23"/>
+      <c r="N36" s="23"/>
+      <c r="O36" s="23"/>
+      <c r="P36" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="Q36" s="30"/>
-      <c r="R36" s="30"/>
-      <c r="S36" s="30"/>
-      <c r="T36" s="30"/>
-      <c r="U36" s="30"/>
-      <c r="V36" s="31"/>
+      <c r="Q36" s="23"/>
+      <c r="R36" s="23"/>
+      <c r="S36" s="23"/>
+      <c r="T36" s="23"/>
+      <c r="U36" s="23"/>
+      <c r="V36" s="24"/>
     </row>
     <row r="37" spans="1:22" ht="114" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="32"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="53" t="s">
-        <v>64</v>
-      </c>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="25"/>
-      <c r="I37" s="25"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="L37" s="25"/>
-      <c r="M37" s="25"/>
-      <c r="N37" s="25"/>
-      <c r="O37" s="25"/>
-      <c r="P37" s="75" t="s">
+      <c r="A37" s="78" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="77" t="s">
+        <v>67</v>
+      </c>
+      <c r="E37" s="47"/>
+      <c r="F37" s="47"/>
+      <c r="G37" s="47"/>
+      <c r="H37" s="47"/>
+      <c r="I37" s="47"/>
+      <c r="J37" s="47"/>
+      <c r="K37" s="67" t="s">
+        <v>68</v>
+      </c>
+      <c r="L37" s="23"/>
+      <c r="M37" s="23"/>
+      <c r="N37" s="23"/>
+      <c r="O37" s="23"/>
+      <c r="P37" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="Q37" s="25"/>
-      <c r="R37" s="25"/>
-      <c r="S37" s="25"/>
-      <c r="T37" s="25"/>
-      <c r="U37" s="25"/>
-      <c r="V37" s="26"/>
+      <c r="Q37" s="23"/>
+      <c r="R37" s="23"/>
+      <c r="S37" s="23"/>
+      <c r="T37" s="23"/>
+      <c r="U37" s="23"/>
+      <c r="V37" s="24"/>
     </row>
     <row r="38" spans="1:22" ht="114" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="50" t="s">
-        <v>66</v>
-      </c>
-      <c r="B38" s="25"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="68" t="s">
-        <v>67</v>
-      </c>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
-      <c r="J38" s="22"/>
-      <c r="K38" s="46" t="s">
-        <v>68</v>
-      </c>
-      <c r="L38" s="25"/>
-      <c r="M38" s="25"/>
-      <c r="N38" s="25"/>
-      <c r="O38" s="25"/>
-      <c r="P38" s="75" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q38" s="25"/>
-      <c r="R38" s="25"/>
-      <c r="S38" s="25"/>
-      <c r="T38" s="25"/>
-      <c r="U38" s="25"/>
-      <c r="V38" s="26"/>
+      <c r="A38" s="67" t="s">
+        <v>69</v>
+      </c>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="23"/>
+      <c r="J38" s="24"/>
+      <c r="K38" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="L38" s="23"/>
+      <c r="M38" s="23"/>
+      <c r="N38" s="23"/>
+      <c r="O38" s="23"/>
+      <c r="P38" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q38" s="23"/>
+      <c r="R38" s="23"/>
+      <c r="S38" s="23"/>
+      <c r="T38" s="23"/>
+      <c r="U38" s="23"/>
+      <c r="V38" s="24"/>
     </row>
     <row r="39" spans="1:22" ht="114" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="46" t="s">
-        <v>69</v>
-      </c>
-      <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="25"/>
-      <c r="I39" s="25"/>
-      <c r="J39" s="26"/>
-      <c r="K39" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="L39" s="25"/>
-      <c r="M39" s="25"/>
-      <c r="N39" s="25"/>
-      <c r="O39" s="25"/>
-      <c r="P39" s="56" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q39" s="25"/>
-      <c r="R39" s="25"/>
-      <c r="S39" s="25"/>
-      <c r="T39" s="25"/>
-      <c r="U39" s="25"/>
-      <c r="V39" s="26"/>
+      <c r="A39" s="78" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="23"/>
+      <c r="H39" s="23"/>
+      <c r="I39" s="23"/>
+      <c r="J39" s="24"/>
+      <c r="K39" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="L39" s="23"/>
+      <c r="M39" s="23"/>
+      <c r="N39" s="23"/>
+      <c r="O39" s="23"/>
+      <c r="P39" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q39" s="23"/>
+      <c r="R39" s="23"/>
+      <c r="S39" s="23"/>
+      <c r="T39" s="23"/>
+      <c r="U39" s="23"/>
+      <c r="V39" s="24"/>
     </row>
     <row r="40" spans="1:22" ht="114" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="50" t="s">
-        <v>73</v>
-      </c>
-      <c r="B40" s="25"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="84" t="s">
-        <v>74</v>
-      </c>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
-      <c r="I40" s="25"/>
-      <c r="J40" s="26"/>
-      <c r="K40" s="64" t="s">
-        <v>75</v>
-      </c>
-      <c r="L40" s="25"/>
-      <c r="M40" s="25"/>
-      <c r="N40" s="25"/>
-      <c r="O40" s="25"/>
-      <c r="P40" s="69" t="s">
+      <c r="A40" s="67" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="23"/>
+      <c r="J40" s="24"/>
+      <c r="K40" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="L40" s="23"/>
+      <c r="M40" s="23"/>
+      <c r="N40" s="23"/>
+      <c r="O40" s="23"/>
+      <c r="P40" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="Q40" s="25"/>
-      <c r="R40" s="25"/>
-      <c r="S40" s="25"/>
-      <c r="T40" s="25"/>
-      <c r="U40" s="25"/>
-      <c r="V40" s="26"/>
+      <c r="Q40" s="23"/>
+      <c r="R40" s="23"/>
+      <c r="S40" s="23"/>
+      <c r="T40" s="23"/>
+      <c r="U40" s="23"/>
+      <c r="V40" s="24"/>
     </row>
     <row r="41" spans="1:22" ht="114" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="B41" s="25"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="75" t="s">
-        <v>78</v>
-      </c>
-      <c r="E41" s="25"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="25"/>
-      <c r="I41" s="25"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="64" t="s">
-        <v>79</v>
-      </c>
-      <c r="L41" s="25"/>
-      <c r="M41" s="25"/>
-      <c r="N41" s="25"/>
-      <c r="O41" s="25"/>
-      <c r="P41" s="69" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q41" s="25"/>
-      <c r="R41" s="25"/>
-      <c r="S41" s="25"/>
-      <c r="T41" s="25"/>
-      <c r="U41" s="25"/>
-      <c r="V41" s="26"/>
-    </row>
-    <row r="42" spans="1:22" ht="114" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="46" t="s">
+      <c r="A41" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="25"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="75" t="s">
+      <c r="B41" s="23"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
-      <c r="I42" s="25"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="64" t="s">
+      <c r="E41" s="23"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="23"/>
+      <c r="J41" s="24"/>
+      <c r="K41" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="L42" s="25"/>
-      <c r="M42" s="25"/>
-      <c r="N42" s="25"/>
-      <c r="O42" s="25"/>
-      <c r="P42" s="69" t="s">
+      <c r="L41" s="23"/>
+      <c r="M41" s="23"/>
+      <c r="N41" s="23"/>
+      <c r="O41" s="23"/>
+      <c r="P41" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="Q42" s="25"/>
-      <c r="R42" s="25"/>
-      <c r="S42" s="25"/>
-      <c r="T42" s="25"/>
-      <c r="U42" s="25"/>
-      <c r="V42" s="26"/>
-    </row>
-    <row r="43" spans="1:22" s="2" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A43" s="57" t="s">
+      <c r="Q41" s="23"/>
+      <c r="R41" s="23"/>
+      <c r="S41" s="23"/>
+      <c r="T41" s="23"/>
+      <c r="U41" s="23"/>
+      <c r="V41" s="24"/>
+    </row>
+    <row r="42" spans="1:22" s="2" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A42" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="B43" s="25"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="26"/>
-      <c r="G43" s="77" t="s">
+      <c r="B42" s="23"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="H43" s="25"/>
-      <c r="I43" s="25"/>
-      <c r="J43" s="25"/>
-      <c r="K43" s="25"/>
-      <c r="L43" s="25"/>
-      <c r="M43" s="25"/>
-      <c r="N43" s="25"/>
-      <c r="O43" s="26"/>
-      <c r="P43" s="77" t="s">
+      <c r="H42" s="23"/>
+      <c r="I42" s="23"/>
+      <c r="J42" s="23"/>
+      <c r="K42" s="23"/>
+      <c r="L42" s="23"/>
+      <c r="M42" s="23"/>
+      <c r="N42" s="23"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="Q43" s="25"/>
-      <c r="R43" s="25"/>
-      <c r="S43" s="25"/>
-      <c r="T43" s="25"/>
-      <c r="U43" s="25"/>
-      <c r="V43" s="26"/>
+      <c r="Q42" s="23"/>
+      <c r="R42" s="23"/>
+      <c r="S42" s="23"/>
+      <c r="T42" s="23"/>
+      <c r="U42" s="23"/>
+      <c r="V42" s="24"/>
+    </row>
+    <row r="43" spans="1:22" ht="114" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="81" t="s">
+        <v>86</v>
+      </c>
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="82"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="23"/>
+      <c r="J43" s="23"/>
+      <c r="K43" s="23"/>
+      <c r="L43" s="23"/>
+      <c r="M43" s="23"/>
+      <c r="N43" s="23"/>
+      <c r="O43" s="24"/>
+      <c r="P43" s="22"/>
+      <c r="Q43" s="23"/>
+      <c r="R43" s="23"/>
+      <c r="S43" s="23"/>
+      <c r="T43" s="23"/>
+      <c r="U43" s="23"/>
+      <c r="V43" s="24"/>
     </row>
     <row r="44" spans="1:22" ht="114" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="49" t="s">
-        <v>86</v>
-      </c>
-      <c r="B44" s="25"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="26"/>
-      <c r="G44" s="51"/>
-      <c r="H44" s="25"/>
-      <c r="I44" s="25"/>
-      <c r="J44" s="25"/>
-      <c r="K44" s="25"/>
-      <c r="L44" s="25"/>
-      <c r="M44" s="25"/>
-      <c r="N44" s="25"/>
-      <c r="O44" s="26"/>
-      <c r="P44" s="35"/>
-      <c r="Q44" s="25"/>
-      <c r="R44" s="25"/>
-      <c r="S44" s="25"/>
-      <c r="T44" s="25"/>
-      <c r="U44" s="25"/>
-      <c r="V44" s="26"/>
-    </row>
-    <row r="45" spans="1:22" ht="114" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="49" t="s">
+      <c r="A44" s="81" t="s">
         <v>87</v>
       </c>
-      <c r="B45" s="25"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="26"/>
-      <c r="G45" s="35"/>
-      <c r="H45" s="25"/>
-      <c r="I45" s="25"/>
-      <c r="J45" s="25"/>
-      <c r="K45" s="25"/>
-      <c r="L45" s="25"/>
-      <c r="M45" s="25"/>
-      <c r="N45" s="25"/>
-      <c r="O45" s="26"/>
-      <c r="P45" s="35"/>
-      <c r="Q45" s="25"/>
-      <c r="R45" s="25"/>
-      <c r="S45" s="25"/>
-      <c r="T45" s="25"/>
-      <c r="U45" s="25"/>
-      <c r="V45" s="26"/>
-    </row>
-    <row r="46" spans="1:22" s="2" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A46" s="57" t="s">
+      <c r="B44" s="23"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="23"/>
+      <c r="I44" s="23"/>
+      <c r="J44" s="23"/>
+      <c r="K44" s="23"/>
+      <c r="L44" s="23"/>
+      <c r="M44" s="23"/>
+      <c r="N44" s="23"/>
+      <c r="O44" s="24"/>
+      <c r="P44" s="22"/>
+      <c r="Q44" s="23"/>
+      <c r="R44" s="23"/>
+      <c r="S44" s="23"/>
+      <c r="T44" s="23"/>
+      <c r="U44" s="23"/>
+      <c r="V44" s="24"/>
+    </row>
+    <row r="45" spans="1:22" s="2" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A45" s="59" t="s">
         <v>88</v>
       </c>
-      <c r="B46" s="25"/>
-      <c r="C46" s="25"/>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25"/>
-      <c r="H46" s="25"/>
-      <c r="I46" s="25"/>
-      <c r="J46" s="25"/>
-      <c r="K46" s="25"/>
-      <c r="L46" s="25"/>
-      <c r="M46" s="25"/>
-      <c r="N46" s="25"/>
-      <c r="O46" s="25"/>
-      <c r="P46" s="25"/>
-      <c r="Q46" s="25"/>
-      <c r="R46" s="25"/>
-      <c r="S46" s="25"/>
-      <c r="T46" s="25"/>
-      <c r="U46" s="25"/>
-      <c r="V46" s="26"/>
-    </row>
-    <row r="607" spans="1:22" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A607" s="57" t="s">
+      <c r="B45" s="23"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="23"/>
+      <c r="G45" s="23"/>
+      <c r="H45" s="23"/>
+      <c r="I45" s="23"/>
+      <c r="J45" s="23"/>
+      <c r="K45" s="23"/>
+      <c r="L45" s="23"/>
+      <c r="M45" s="23"/>
+      <c r="N45" s="23"/>
+      <c r="O45" s="23"/>
+      <c r="P45" s="23"/>
+      <c r="Q45" s="23"/>
+      <c r="R45" s="23"/>
+      <c r="S45" s="23"/>
+      <c r="T45" s="23"/>
+      <c r="U45" s="23"/>
+      <c r="V45" s="24"/>
+    </row>
+    <row r="606" spans="1:22" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A606" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="B607" s="25"/>
-      <c r="C607" s="25"/>
-      <c r="D607" s="25"/>
-      <c r="E607" s="25"/>
-      <c r="F607" s="25"/>
-      <c r="G607" s="25"/>
-      <c r="H607" s="25"/>
-      <c r="I607" s="25"/>
-      <c r="J607" s="25"/>
-      <c r="K607" s="25"/>
-      <c r="L607" s="25"/>
-      <c r="M607" s="25"/>
-      <c r="N607" s="25"/>
-      <c r="O607" s="25"/>
-      <c r="P607" s="25"/>
-      <c r="Q607" s="25"/>
-      <c r="R607" s="25"/>
-      <c r="S607" s="25"/>
-      <c r="T607" s="25"/>
-      <c r="U607" s="25"/>
-      <c r="V607" s="26"/>
+      <c r="B606" s="23"/>
+      <c r="C606" s="23"/>
+      <c r="D606" s="23"/>
+      <c r="E606" s="23"/>
+      <c r="F606" s="23"/>
+      <c r="G606" s="23"/>
+      <c r="H606" s="23"/>
+      <c r="I606" s="23"/>
+      <c r="J606" s="23"/>
+      <c r="K606" s="23"/>
+      <c r="L606" s="23"/>
+      <c r="M606" s="23"/>
+      <c r="N606" s="23"/>
+      <c r="O606" s="23"/>
+      <c r="P606" s="23"/>
+      <c r="Q606" s="23"/>
+      <c r="R606" s="23"/>
+      <c r="S606" s="23"/>
+      <c r="T606" s="23"/>
+      <c r="U606" s="23"/>
+      <c r="V606" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="194">
+  <mergeCells count="189">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="P18:V18"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="S1:U2"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="S11:T11"/>
     <mergeCell ref="P44:V44"/>
+    <mergeCell ref="P16:V16"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A27:O27"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I9:I11"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="M9:N10"/>
+    <mergeCell ref="O9:P10"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="U11:V11"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="K37:O37"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D34:J34"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A14:V14"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="Q12:R13"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="K34:O34"/>
+    <mergeCell ref="G43:O43"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="L29:O29"/>
+    <mergeCell ref="D36:J36"/>
+    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="V7:V8"/>
+    <mergeCell ref="E9:G10"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A3:C4"/>
+    <mergeCell ref="D35:J35"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="P27:V27"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="A25:O25"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="P22:V22"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="P25:V25"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="P15:V15"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A606:V606"/>
+    <mergeCell ref="A23:V23"/>
+    <mergeCell ref="K39:O39"/>
+    <mergeCell ref="H1:I2"/>
+    <mergeCell ref="J1:K2"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="K41:O41"/>
+    <mergeCell ref="R30:U30"/>
+    <mergeCell ref="M33:U33"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="P35:V35"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A31:V31"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="D37:J37"/>
     <mergeCell ref="P39:V39"/>
-    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A35:C36"/>
+    <mergeCell ref="N15:O15"/>
     <mergeCell ref="P41:V41"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="M33:U33"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="P38:V38"/>
-    <mergeCell ref="E34:J34"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="E30:K30"/>
+    <mergeCell ref="D1:G2"/>
+    <mergeCell ref="P34:V34"/>
+    <mergeCell ref="V1:V2"/>
+    <mergeCell ref="K38:O38"/>
+    <mergeCell ref="E32:J32"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="B12:C13"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="P21:V21"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K35:O35"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="A20:V20"/>
+    <mergeCell ref="P36:V36"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="E29:K29"/>
+    <mergeCell ref="A17:V17"/>
+    <mergeCell ref="A28:V28"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="G44:O44"/>
+    <mergeCell ref="G42:O42"/>
+    <mergeCell ref="F7:G8"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="A45:V45"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="L3:V3"/>
+    <mergeCell ref="P24:V24"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="U9:V10"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="S12:T13"/>
+    <mergeCell ref="B9:C10"/>
+    <mergeCell ref="P19:V19"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="D38:J38"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="N19:O19"/>
     <mergeCell ref="D40:J40"/>
-    <mergeCell ref="P43:V43"/>
-    <mergeCell ref="K41:O41"/>
+    <mergeCell ref="D41:J41"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="F5:G6"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="Q9:R10"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="R29:U29"/>
+    <mergeCell ref="P26:V26"/>
+    <mergeCell ref="U12:V13"/>
+    <mergeCell ref="A26:O26"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="S9:T10"/>
+    <mergeCell ref="M11:N11"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="R7:R8"/>
     <mergeCell ref="I7:I8"/>
@@ -2944,286 +3057,144 @@
     <mergeCell ref="M12:N13"/>
     <mergeCell ref="O12:P13"/>
     <mergeCell ref="L21:M21"/>
-    <mergeCell ref="A31:D31"/>
     <mergeCell ref="Q11:R11"/>
     <mergeCell ref="O11:P11"/>
     <mergeCell ref="H12:H13"/>
     <mergeCell ref="J12:J13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="F5:G6"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="Q9:R10"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="R29:U29"/>
-    <mergeCell ref="P26:V26"/>
-    <mergeCell ref="U12:V13"/>
-    <mergeCell ref="A26:O26"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="G45:O45"/>
-    <mergeCell ref="G43:O43"/>
-    <mergeCell ref="F7:G8"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="A46:V46"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="L3:V3"/>
-    <mergeCell ref="P24:V24"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="L31:O31"/>
-    <mergeCell ref="U9:V10"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="U4:V4"/>
-    <mergeCell ref="S12:T13"/>
-    <mergeCell ref="B9:C10"/>
-    <mergeCell ref="P19:V19"/>
-    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="P43:V43"/>
+    <mergeCell ref="P38:V38"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="P40:V40"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="M32:U32"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="E33:J33"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="E30:K30"/>
     <mergeCell ref="D39:J39"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="D41:J41"/>
-    <mergeCell ref="D42:J42"/>
-    <mergeCell ref="V1:V2"/>
-    <mergeCell ref="K39:O39"/>
-    <mergeCell ref="E33:J33"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="B12:C13"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="P21:V21"/>
-    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="P42:V42"/>
+    <mergeCell ref="K40:O40"/>
     <mergeCell ref="K36:O36"/>
-    <mergeCell ref="P31:Q31"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="A20:V20"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="E29:K29"/>
-    <mergeCell ref="A17:V17"/>
-    <mergeCell ref="A28:V28"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="A607:V607"/>
-    <mergeCell ref="A23:V23"/>
-    <mergeCell ref="K40:O40"/>
-    <mergeCell ref="H1:I2"/>
-    <mergeCell ref="J1:K2"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="K42:O42"/>
-    <mergeCell ref="R30:U30"/>
-    <mergeCell ref="M34:U34"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="P36:V36"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A32:V32"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="D38:J38"/>
-    <mergeCell ref="P40:V40"/>
-    <mergeCell ref="A36:C37"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="R31:U31"/>
-    <mergeCell ref="P42:V42"/>
-    <mergeCell ref="D1:G2"/>
-    <mergeCell ref="P35:V35"/>
-    <mergeCell ref="S9:T10"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="K37:O37"/>
-    <mergeCell ref="A3:C4"/>
-    <mergeCell ref="D36:J36"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="P27:V27"/>
-    <mergeCell ref="L30:O30"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="A25:O25"/>
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="P22:V22"/>
-    <mergeCell ref="P30:Q30"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="P25:V25"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="P15:V15"/>
-    <mergeCell ref="E31:K31"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D35:J35"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A14:V14"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="Q12:R13"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="K35:O35"/>
-    <mergeCell ref="G44:O44"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="L29:O29"/>
-    <mergeCell ref="D37:J37"/>
-    <mergeCell ref="T7:T8"/>
-    <mergeCell ref="V7:V8"/>
-    <mergeCell ref="E9:G10"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="P18:V18"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="S1:U2"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="P45:V45"/>
-    <mergeCell ref="P16:V16"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="P29:Q29"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="A27:O27"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I9:I11"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="M9:N10"/>
-    <mergeCell ref="O9:P10"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="U11:V11"/>
-    <mergeCell ref="T5:T6"/>
-    <mergeCell ref="K38:O38"/>
   </mergeCells>
   <dataValidations count="30">
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=9175.87085811385_x000d__x000a_" sqref="D64465:F64465 CS64438" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=9175.87085811385_x000d__x000a_" sqref="D64464:F64464 CS64437" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=1971.66180968562_x000d__x000a_" sqref="D64477:F64477 CS64450" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=1971.66180968562_x000d__x000a_" sqref="D64476:F64476 CS64449" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=654.21_x000d__x000a_" sqref="D64473:F64473 CS64446" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=654.21_x000d__x000a_" sqref="D64472:F64472 CS64445" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=3831.77570093458_x000d__x000a_" sqref="D64482:F64482 CS64455" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=3831.77570093458_x000d__x000a_" sqref="D64481:F64481 CS64454" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=969_x000d__x000a_" sqref="D64478:F64478 CS64451" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=969_x000d__x000a_" sqref="D64477:F64477 CS64450" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=29778.32_x000d__x000a_" sqref="D64475:F64475 CS64448" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=29778.32_x000d__x000a_" sqref="D64474:F64474 CS64447" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=2730_x000d__x000a_" sqref="D64470:F64470 CS64443" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=2730_x000d__x000a_" sqref="D64469:F64469 CS64442" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=140.186915887849_x000d__x000a_" sqref="D64467:F64467 CS64440" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=140.186915887849_x000d__x000a_" sqref="D64466:F64466 CS64439" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=3495_x000d__x000a_" sqref="D64471:F64471 CS64444" xr:uid="{00000000-0002-0000-0000-000008000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=3495_x000d__x000a_" sqref="D64470:F64470 CS64443" xr:uid="{00000000-0002-0000-0000-000008000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=76.46_x000d__x000a_" sqref="D64466:F64466 CS64439" xr:uid="{00000000-0002-0000-0000-000009000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=76.46_x000d__x000a_" sqref="D64465:F64465 CS64438" xr:uid="{00000000-0002-0000-0000-000009000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:2=0_x000d__x000a_" sqref="D64464:F64464 D64468:F64469 D64472:F64472 D64474:F64474 D64479:F64481 P64464:Q64464 P64468:Q64469 P64472:Q64472 P64474:Q64474 P64477:Q64477 P64479:Q64480 CS64445" xr:uid="{00000000-0002-0000-0000-00000A000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:2=0_x000d__x000a_" sqref="D64463:F64463 D64467:F64468 D64471:F64471 D64473:F64473 D64478:F64480 P64463:Q64463 P64467:Q64468 P64471:Q64471 P64473:Q64473 P64476:Q64476 P64478:Q64479 CS64444" xr:uid="{00000000-0002-0000-0000-00000A000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=3124.44_x000d__x000a_" sqref="P64481:Q64481 DA64454" xr:uid="{00000000-0002-0000-0000-00000B000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=3124.44_x000d__x000a_" sqref="P64480:Q64480 DA64453" xr:uid="{00000000-0002-0000-0000-00000B000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=2947.48_x000d__x000a_" sqref="P64473:Q64473 DA64446" xr:uid="{00000000-0002-0000-0000-00000C000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=2947.48_x000d__x000a_" sqref="P64472:Q64472 DA64445" xr:uid="{00000000-0002-0000-0000-00000C000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=337579.47_x000d__x000a_" sqref="P64475:Q64475 DA64448" xr:uid="{00000000-0002-0000-0000-00000D000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=337579.47_x000d__x000a_" sqref="P64474:Q64474 DA64447" xr:uid="{00000000-0002-0000-0000-00000D000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=3041.07_x000d__x000a_" sqref="P64482:Q64482 DA64455" xr:uid="{00000000-0002-0000-0000-00000E000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=3041.07_x000d__x000a_" sqref="P64481:Q64481 DA64454" xr:uid="{00000000-0002-0000-0000-00000E000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=10387_x000d__x000a_" sqref="P64478:Q64478 DA64451" xr:uid="{00000000-0002-0000-0000-00000F000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=10387_x000d__x000a_" sqref="P64477:Q64477 DA64450" xr:uid="{00000000-0002-0000-0000-00000F000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=7600_x000d__x000a_" sqref="P64471:Q64471 DA64444" xr:uid="{00000000-0002-0000-0000-000010000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=7600_x000d__x000a_" sqref="P64470:Q64470 DA64443" xr:uid="{00000000-0002-0000-0000-000010000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=33859.1606542056_x000d__x000a_" sqref="P64470:Q64470 DA64443" xr:uid="{00000000-0002-0000-0000-000011000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=33859.1606542056_x000d__x000a_" sqref="P64469:Q64469 DA64442" xr:uid="{00000000-0002-0000-0000-000011000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=108462.39_x000d__x000a_" sqref="P64466:Q64466 DA64439" xr:uid="{00000000-0002-0000-0000-000012000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=108462.39_x000d__x000a_" sqref="P64465:Q64465 DA64438" xr:uid="{00000000-0002-0000-0000-000012000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=1064.01962616822_x000d__x000a_" sqref="P64467:Q64467 DA64440" xr:uid="{00000000-0002-0000-0000-000013000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=1064.01962616822_x000d__x000a_" sqref="P64466:Q64466 DA64439" xr:uid="{00000000-0002-0000-0000-000013000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=16849.7162616821_x000d__x000a_" sqref="CX64450" xr:uid="{00000000-0002-0000-0000-000014000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=16849.7162616821_x000d__x000a_" sqref="CX64449" xr:uid="{00000000-0002-0000-0000-000014000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=116642.038971963_x000d__x000a_" sqref="CX64446" xr:uid="{00000000-0002-0000-0000-000015000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=116642.038971963_x000d__x000a_" sqref="CX64445" xr:uid="{00000000-0002-0000-0000-000015000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=379048.61_x000d__x000a_" sqref="CX64448" xr:uid="{00000000-0002-0000-0000-000016000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=379048.61_x000d__x000a_" sqref="CX64447" xr:uid="{00000000-0002-0000-0000-000016000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=1031.37196261682_x000d__x000a_" sqref="CX64440" xr:uid="{00000000-0002-0000-0000-000017000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=1031.37196261682_x000d__x000a_" sqref="CX64439" xr:uid="{00000000-0002-0000-0000-000017000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=57417.1622769754_x000d__x000a_" sqref="CX64438" xr:uid="{00000000-0002-0000-0000-000018000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=57417.1622769754_x000d__x000a_" sqref="CX64437" xr:uid="{00000000-0002-0000-0000-000018000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=78897.0664655905_x000d__x000a_" sqref="CX64444" xr:uid="{00000000-0002-0000-0000-000019000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=78897.0664655905_x000d__x000a_" sqref="CX64443" xr:uid="{00000000-0002-0000-0000-000019000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=812367.264112149_x000d__x000a_" sqref="CX64455" xr:uid="{00000000-0002-0000-0000-00001A000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=812367.264112149_x000d__x000a_" sqref="CX64454" xr:uid="{00000000-0002-0000-0000-00001A000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=7558.54_x000d__x000a_" sqref="CX64451" xr:uid="{00000000-0002-0000-0000-00001B000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=7558.54_x000d__x000a_" sqref="CX64450" xr:uid="{00000000-0002-0000-0000-00001B000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=33220_x000d__x000a_" sqref="CX64443" xr:uid="{00000000-0002-0000-0000-00001C000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=33220_x000d__x000a_" sqref="CX64442" xr:uid="{00000000-0002-0000-0000-00001C000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=65552.82_x000d__x000a_" sqref="CX64439" xr:uid="{00000000-0002-0000-0000-00001D000000}">
+    <dataValidation type="textLength" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="XLBVal:5=65552.82_x000d__x000a_" sqref="CX64438" xr:uid="{00000000-0002-0000-0000-00001D000000}">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
@@ -3232,9 +3203,9 @@
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="12" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="31" max="26" man="1"/>
-    <brk id="328" max="26" man="1"/>
-    <brk id="712" max="26" man="1"/>
+    <brk id="30" max="26" man="1"/>
+    <brk id="327" max="26" man="1"/>
+    <brk id="711" max="26" man="1"/>
   </rowBreaks>
   <drawing r:id="rId2"/>
 </worksheet>
